--- a/NECP Scenario/Results/Regional Results/SAMOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/SAMOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.325991927476777E-08</v>
+        <v>4.900167923176754E-08</v>
       </c>
       <c r="C3">
-        <v>3.343424150313473E-08</v>
+        <v>4.92519257989837E-08</v>
       </c>
       <c r="D3">
-        <v>0.0195995870537325</v>
+        <v>0.0207705689272582</v>
       </c>
       <c r="E3">
-        <v>0.0225285209551822</v>
+        <v>0.0238516933799496</v>
       </c>
       <c r="F3">
-        <v>0.0225285098319308</v>
+        <v>0.0253424198795408</v>
       </c>
       <c r="G3">
-        <v>0.053820457842673</v>
+        <v>0.0530897093733069</v>
       </c>
       <c r="H3">
-        <v>0.057005730900838</v>
+        <v>0.060459100884085</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000065402</v>
+        <v>0.4000000000071724</v>
       </c>
       <c r="C13">
-        <v>0.4000000000085835</v>
+        <v>0.4000000000101733</v>
       </c>
       <c r="D13">
-        <v>0.4000000000129363</v>
+        <v>0.4000000000156781</v>
       </c>
       <c r="E13">
-        <v>0.4000000000236585</v>
+        <v>0.4000000000289636</v>
       </c>
       <c r="F13">
-        <v>0.4000000000406136</v>
+        <v>0.400000000049842</v>
       </c>
       <c r="G13">
-        <v>0.4000000000748669</v>
+        <v>0.4000000000941192</v>
       </c>
       <c r="H13">
-        <v>0.400000000425575</v>
+        <v>0.4000000005043388</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.0578756740461411</v>
+        <v>0.0592147658342066</v>
       </c>
       <c r="E27">
-        <v>0.0578756750846313</v>
+        <v>0.0592147669089021</v>
       </c>
       <c r="F27">
-        <v>0.0695388021464419</v>
+        <v>0.0709430359501064</v>
       </c>
       <c r="G27">
-        <v>0.1185990546227552</v>
+        <v>0.104043023605149</v>
       </c>
       <c r="H27">
-        <v>0.1276466667512566</v>
+        <v>0.1238652296873802</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3.842147272039209E-08</v>
+        <v>5.746370870567501E-08</v>
       </c>
       <c r="E29">
-        <v>8.097628527088644E-07</v>
+        <v>0.0195887859477102</v>
       </c>
       <c r="F29">
-        <v>0.0271028336735133</v>
+        <v>0.0306552926886172</v>
       </c>
       <c r="G29">
-        <v>0.0325540443518248</v>
+        <v>0.0325540443784634</v>
       </c>
       <c r="H29">
-        <v>0.0325540447685582</v>
+        <v>0.0325540447608508</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.0195088017934369</v>
+        <v>0.0188409031945748</v>
       </c>
       <c r="E33">
-        <v>0.1241718982481138</v>
+        <v>0.1147075487799967</v>
       </c>
       <c r="F33">
-        <v>0.1341361460246117</v>
+        <v>0.127960741222067</v>
       </c>
       <c r="G33">
-        <v>0.1361569026793901</v>
+        <v>0.1279607478667115</v>
       </c>
       <c r="H33">
-        <v>0.1361569166717344</v>
+        <v>0.1304213881939245</v>
       </c>
     </row>
     <row r="34" spans="1:8">
